--- a/artfynd/A 56632-2024 artfynd.xlsx
+++ b/artfynd/A 56632-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122646803</v>
+        <v>122646819</v>
       </c>
       <c r="B2" t="n">
-        <v>94641</v>
+        <v>78656</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550560</v>
+        <v>550649</v>
       </c>
       <c r="R2" t="n">
-        <v>7244169</v>
+        <v>7244482</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122646806</v>
+        <v>122646802</v>
       </c>
       <c r="B3" t="n">
         <v>74757</v>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550584</v>
+        <v>550583</v>
       </c>
       <c r="R3" t="n">
-        <v>7244283</v>
+        <v>7244155</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122646805</v>
+        <v>122646799</v>
       </c>
       <c r="B4" t="n">
-        <v>74741</v>
+        <v>79766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6439</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550565</v>
+        <v>550558</v>
       </c>
       <c r="R4" t="n">
-        <v>7244209</v>
+        <v>7244160</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122646819</v>
+        <v>122646801</v>
       </c>
       <c r="B5" t="n">
         <v>78656</v>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>550649</v>
+        <v>550582</v>
       </c>
       <c r="R5" t="n">
-        <v>7244482</v>
+        <v>7244157</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122646804</v>
+        <v>122646803</v>
       </c>
       <c r="B6" t="n">
-        <v>90829</v>
+        <v>94641</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>2809</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550563</v>
+        <v>550560</v>
       </c>
       <c r="R6" t="n">
-        <v>7244202</v>
+        <v>7244169</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122646802</v>
+        <v>122646804</v>
       </c>
       <c r="B7" t="n">
-        <v>74757</v>
+        <v>90829</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550583</v>
+        <v>550563</v>
       </c>
       <c r="R7" t="n">
-        <v>7244155</v>
+        <v>7244202</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122646807</v>
+        <v>122646800</v>
       </c>
       <c r="B8" t="n">
-        <v>57383</v>
+        <v>90851</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550585</v>
+        <v>550574</v>
       </c>
       <c r="R8" t="n">
-        <v>7244284</v>
+        <v>7244164</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,11 +1387,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122646800</v>
+        <v>122646798</v>
       </c>
       <c r="B9" t="n">
         <v>90851</v>
@@ -1462,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550574</v>
+        <v>550534</v>
       </c>
       <c r="R9" t="n">
-        <v>7244164</v>
+        <v>7244163</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122646799</v>
+        <v>122646807</v>
       </c>
       <c r="B10" t="n">
-        <v>79766</v>
+        <v>57383</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550558</v>
+        <v>550585</v>
       </c>
       <c r="R10" t="n">
-        <v>7244160</v>
+        <v>7244284</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,6 +1599,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122646798</v>
+        <v>122646809</v>
       </c>
       <c r="B11" t="n">
-        <v>90851</v>
+        <v>78656</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,21 +1650,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550534</v>
+        <v>550583</v>
       </c>
       <c r="R11" t="n">
-        <v>7244163</v>
+        <v>7244281</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122646809</v>
+        <v>122646805</v>
       </c>
       <c r="B12" t="n">
-        <v>78656</v>
+        <v>74741</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,25 +1752,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550583</v>
+        <v>550565</v>
       </c>
       <c r="R12" t="n">
-        <v>7244281</v>
+        <v>7244209</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122646801</v>
+        <v>122646806</v>
       </c>
       <c r="B13" t="n">
-        <v>78656</v>
+        <v>74757</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,21 +1862,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550582</v>
+        <v>550584</v>
       </c>
       <c r="R13" t="n">
-        <v>7244157</v>
+        <v>7244283</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 56632-2024 artfynd.xlsx
+++ b/artfynd/A 56632-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122646819</v>
+        <v>122646804</v>
       </c>
       <c r="B2" t="n">
-        <v>78656</v>
+        <v>90830</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550649</v>
+        <v>550563</v>
       </c>
       <c r="R2" t="n">
-        <v>7244482</v>
+        <v>7244202</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122646802</v>
+        <v>122646803</v>
       </c>
       <c r="B3" t="n">
-        <v>74757</v>
+        <v>94642</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>2809</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550583</v>
+        <v>550560</v>
       </c>
       <c r="R3" t="n">
-        <v>7244155</v>
+        <v>7244169</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +890,7 @@
         <v>122646799</v>
       </c>
       <c r="B4" t="n">
-        <v>79766</v>
+        <v>79767</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122646801</v>
+        <v>122646819</v>
       </c>
       <c r="B5" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>550582</v>
+        <v>550649</v>
       </c>
       <c r="R5" t="n">
-        <v>7244157</v>
+        <v>7244482</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122646803</v>
+        <v>122646806</v>
       </c>
       <c r="B6" t="n">
-        <v>94641</v>
+        <v>74758</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2809</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550560</v>
+        <v>550584</v>
       </c>
       <c r="R6" t="n">
-        <v>7244169</v>
+        <v>7244283</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122646804</v>
+        <v>122646802</v>
       </c>
       <c r="B7" t="n">
-        <v>90829</v>
+        <v>74758</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550563</v>
+        <v>550583</v>
       </c>
       <c r="R7" t="n">
-        <v>7244202</v>
+        <v>7244155</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122646800</v>
+        <v>122646809</v>
       </c>
       <c r="B8" t="n">
-        <v>90851</v>
+        <v>78657</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550574</v>
+        <v>550583</v>
       </c>
       <c r="R8" t="n">
-        <v>7244164</v>
+        <v>7244281</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122646798</v>
+        <v>122646800</v>
       </c>
       <c r="B9" t="n">
-        <v>90851</v>
+        <v>90852</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550534</v>
+        <v>550574</v>
       </c>
       <c r="R9" t="n">
-        <v>7244163</v>
+        <v>7244164</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,7 +1526,7 @@
         <v>122646807</v>
       </c>
       <c r="B10" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122646809</v>
+        <v>122646801</v>
       </c>
       <c r="B11" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550583</v>
+        <v>550582</v>
       </c>
       <c r="R11" t="n">
-        <v>7244281</v>
+        <v>7244157</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122646805</v>
+        <v>122646798</v>
       </c>
       <c r="B12" t="n">
-        <v>74741</v>
+        <v>90852</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,25 +1752,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550565</v>
+        <v>550534</v>
       </c>
       <c r="R12" t="n">
-        <v>7244209</v>
+        <v>7244163</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122646806</v>
+        <v>122646805</v>
       </c>
       <c r="B13" t="n">
-        <v>74757</v>
+        <v>74742</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,25 +1858,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6439</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550584</v>
+        <v>550565</v>
       </c>
       <c r="R13" t="n">
-        <v>7244283</v>
+        <v>7244209</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 56632-2024 artfynd.xlsx
+++ b/artfynd/A 56632-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122646804</v>
+        <v>122646805</v>
       </c>
       <c r="B2" t="n">
-        <v>90830</v>
+        <v>74745</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>6439</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550563</v>
+        <v>550565</v>
       </c>
       <c r="R2" t="n">
-        <v>7244202</v>
+        <v>7244209</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,7 +784,7 @@
         <v>122646803</v>
       </c>
       <c r="B3" t="n">
-        <v>94642</v>
+        <v>94645</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>122646799</v>
       </c>
       <c r="B4" t="n">
-        <v>79767</v>
+        <v>79770</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122646819</v>
+        <v>122646804</v>
       </c>
       <c r="B5" t="n">
-        <v>78657</v>
+        <v>90833</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>550649</v>
+        <v>550563</v>
       </c>
       <c r="R5" t="n">
-        <v>7244482</v>
+        <v>7244202</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122646806</v>
+        <v>122646798</v>
       </c>
       <c r="B6" t="n">
-        <v>74758</v>
+        <v>90855</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550584</v>
+        <v>550534</v>
       </c>
       <c r="R6" t="n">
-        <v>7244283</v>
+        <v>7244163</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122646802</v>
+        <v>122646801</v>
       </c>
       <c r="B7" t="n">
-        <v>74758</v>
+        <v>78660</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550583</v>
+        <v>550582</v>
       </c>
       <c r="R7" t="n">
-        <v>7244155</v>
+        <v>7244157</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122646809</v>
+        <v>122646800</v>
       </c>
       <c r="B8" t="n">
-        <v>78657</v>
+        <v>90855</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550583</v>
+        <v>550574</v>
       </c>
       <c r="R8" t="n">
-        <v>7244281</v>
+        <v>7244164</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122646800</v>
+        <v>122646806</v>
       </c>
       <c r="B9" t="n">
-        <v>90852</v>
+        <v>74761</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550574</v>
+        <v>550584</v>
       </c>
       <c r="R9" t="n">
-        <v>7244164</v>
+        <v>7244283</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122646807</v>
+        <v>122646819</v>
       </c>
       <c r="B10" t="n">
-        <v>57384</v>
+        <v>78660</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550585</v>
+        <v>550649</v>
       </c>
       <c r="R10" t="n">
-        <v>7244284</v>
+        <v>7244482</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1599,11 +1599,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1634,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122646801</v>
+        <v>122646802</v>
       </c>
       <c r="B11" t="n">
-        <v>78657</v>
+        <v>74761</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550582</v>
+        <v>550583</v>
       </c>
       <c r="R11" t="n">
-        <v>7244157</v>
+        <v>7244155</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122646798</v>
+        <v>122646809</v>
       </c>
       <c r="B12" t="n">
-        <v>90852</v>
+        <v>78660</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550534</v>
+        <v>550583</v>
       </c>
       <c r="R12" t="n">
-        <v>7244163</v>
+        <v>7244281</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122646805</v>
+        <v>122646807</v>
       </c>
       <c r="B13" t="n">
-        <v>74742</v>
+        <v>57384</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,25 +1853,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550565</v>
+        <v>550585</v>
       </c>
       <c r="R13" t="n">
-        <v>7244209</v>
+        <v>7244284</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,6 +1917,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 56632-2024 artfynd.xlsx
+++ b/artfynd/A 56632-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122646805</v>
+        <v>122646801</v>
       </c>
       <c r="B2" t="n">
-        <v>74745</v>
+        <v>78660</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550565</v>
+        <v>550582</v>
       </c>
       <c r="R2" t="n">
-        <v>7244209</v>
+        <v>7244157</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122646803</v>
+        <v>122646804</v>
       </c>
       <c r="B3" t="n">
-        <v>94645</v>
+        <v>90833</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2809</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550560</v>
+        <v>550563</v>
       </c>
       <c r="R3" t="n">
-        <v>7244169</v>
+        <v>7244202</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122646799</v>
+        <v>122646819</v>
       </c>
       <c r="B4" t="n">
-        <v>79770</v>
+        <v>78660</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550558</v>
+        <v>550649</v>
       </c>
       <c r="R4" t="n">
-        <v>7244160</v>
+        <v>7244482</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122646804</v>
+        <v>122646803</v>
       </c>
       <c r="B5" t="n">
-        <v>90833</v>
+        <v>94645</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>2809</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>550563</v>
+        <v>550560</v>
       </c>
       <c r="R5" t="n">
-        <v>7244202</v>
+        <v>7244169</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122646798</v>
+        <v>122646809</v>
       </c>
       <c r="B6" t="n">
-        <v>90855</v>
+        <v>78660</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550534</v>
+        <v>550583</v>
       </c>
       <c r="R6" t="n">
-        <v>7244163</v>
+        <v>7244281</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122646801</v>
+        <v>122646805</v>
       </c>
       <c r="B7" t="n">
-        <v>78660</v>
+        <v>74745</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550582</v>
+        <v>550565</v>
       </c>
       <c r="R7" t="n">
-        <v>7244157</v>
+        <v>7244209</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122646800</v>
+        <v>122646798</v>
       </c>
       <c r="B8" t="n">
         <v>90855</v>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550574</v>
+        <v>550534</v>
       </c>
       <c r="R8" t="n">
-        <v>7244164</v>
+        <v>7244163</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122646819</v>
+        <v>122646799</v>
       </c>
       <c r="B10" t="n">
-        <v>78660</v>
+        <v>79770</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550649</v>
+        <v>550558</v>
       </c>
       <c r="R10" t="n">
-        <v>7244482</v>
+        <v>7244160</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122646802</v>
+        <v>122646800</v>
       </c>
       <c r="B11" t="n">
-        <v>74761</v>
+        <v>90855</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550583</v>
+        <v>550574</v>
       </c>
       <c r="R11" t="n">
-        <v>7244155</v>
+        <v>7244164</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122646809</v>
+        <v>122646807</v>
       </c>
       <c r="B12" t="n">
-        <v>78660</v>
+        <v>57384</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550583</v>
+        <v>550585</v>
       </c>
       <c r="R12" t="n">
-        <v>7244281</v>
+        <v>7244284</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,6 +1811,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1841,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122646807</v>
+        <v>122646802</v>
       </c>
       <c r="B13" t="n">
-        <v>57384</v>
+        <v>74761</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1862,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550585</v>
+        <v>550583</v>
       </c>
       <c r="R13" t="n">
-        <v>7244284</v>
+        <v>7244155</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,11 +1922,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 56632-2024 artfynd.xlsx
+++ b/artfynd/A 56632-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122646806</v>
+        <v>122646819</v>
       </c>
       <c r="B2" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550584</v>
+        <v>550649</v>
       </c>
       <c r="R2" t="n">
-        <v>7244283</v>
+        <v>7244482</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122646799</v>
+        <v>122646800</v>
       </c>
       <c r="B3" t="n">
-        <v>79872</v>
+        <v>90962</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550558</v>
+        <v>550574</v>
       </c>
       <c r="R3" t="n">
-        <v>7244160</v>
+        <v>7244164</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122646800</v>
+        <v>122646809</v>
       </c>
       <c r="B4" t="n">
-        <v>90958</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550574</v>
+        <v>550583</v>
       </c>
       <c r="R4" t="n">
-        <v>7244164</v>
+        <v>7244281</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122646807</v>
+        <v>122646798</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>550585</v>
+        <v>550534</v>
       </c>
       <c r="R5" t="n">
-        <v>7244284</v>
+        <v>7244163</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1069,11 +1069,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122646805</v>
+        <v>122646807</v>
       </c>
       <c r="B6" t="n">
-        <v>74847</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550565</v>
+        <v>550585</v>
       </c>
       <c r="R6" t="n">
-        <v>7244209</v>
+        <v>7244284</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,6 +1175,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122646802</v>
+        <v>122646805</v>
       </c>
       <c r="B7" t="n">
-        <v>74863</v>
+        <v>74847</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,25 +1222,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>6439</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550583</v>
+        <v>550565</v>
       </c>
       <c r="R7" t="n">
-        <v>7244155</v>
+        <v>7244209</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122646798</v>
+        <v>122646806</v>
       </c>
       <c r="B8" t="n">
-        <v>90958</v>
+        <v>74863</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550534</v>
+        <v>550584</v>
       </c>
       <c r="R8" t="n">
-        <v>7244163</v>
+        <v>7244283</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122646819</v>
+        <v>122646801</v>
       </c>
       <c r="B9" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550649</v>
+        <v>550582</v>
       </c>
       <c r="R9" t="n">
-        <v>7244482</v>
+        <v>7244157</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122646803</v>
+        <v>122646799</v>
       </c>
       <c r="B10" t="n">
-        <v>94748</v>
+        <v>79876</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,21 +1544,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2809</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550560</v>
+        <v>550558</v>
       </c>
       <c r="R10" t="n">
-        <v>7244169</v>
+        <v>7244160</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1637,7 +1637,7 @@
         <v>122646804</v>
       </c>
       <c r="B11" t="n">
-        <v>90936</v>
+        <v>90940</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1740,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122646809</v>
+        <v>122646803</v>
       </c>
       <c r="B12" t="n">
-        <v>78762</v>
+        <v>94756</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,25 +1752,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550583</v>
+        <v>550560</v>
       </c>
       <c r="R12" t="n">
-        <v>7244281</v>
+        <v>7244169</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122646801</v>
+        <v>122646802</v>
       </c>
       <c r="B13" t="n">
-        <v>78762</v>
+        <v>74863</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,21 +1862,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550582</v>
+        <v>550583</v>
       </c>
       <c r="R13" t="n">
-        <v>7244157</v>
+        <v>7244155</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 56632-2024 artfynd.xlsx
+++ b/artfynd/A 56632-2024 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122646809</v>
+        <v>122646807</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550583</v>
+        <v>550585</v>
       </c>
       <c r="R4" t="n">
-        <v>7244281</v>
+        <v>7244284</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,6 +963,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122646798</v>
+        <v>122646809</v>
       </c>
       <c r="B5" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1014,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>550534</v>
+        <v>550583</v>
       </c>
       <c r="R5" t="n">
-        <v>7244163</v>
+        <v>7244281</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122646807</v>
+        <v>122646798</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1120,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550585</v>
+        <v>550534</v>
       </c>
       <c r="R6" t="n">
-        <v>7244284</v>
+        <v>7244163</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,11 +1180,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 56632-2024 artfynd.xlsx
+++ b/artfynd/A 56632-2024 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122646800</v>
+        <v>122646804</v>
       </c>
       <c r="B3" t="n">
-        <v>90962</v>
+        <v>90940</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550574</v>
+        <v>550563</v>
       </c>
       <c r="R3" t="n">
-        <v>7244164</v>
+        <v>7244202</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122646807</v>
+        <v>122646805</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>74847</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550585</v>
+        <v>550565</v>
       </c>
       <c r="R4" t="n">
-        <v>7244284</v>
+        <v>7244209</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,11 +963,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122646809</v>
+        <v>122646799</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>550583</v>
+        <v>550558</v>
       </c>
       <c r="R5" t="n">
-        <v>7244281</v>
+        <v>7244160</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122646798</v>
+        <v>122646803</v>
       </c>
       <c r="B6" t="n">
-        <v>90962</v>
+        <v>94756</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>2809</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550534</v>
+        <v>550560</v>
       </c>
       <c r="R6" t="n">
-        <v>7244163</v>
+        <v>7244169</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122646805</v>
+        <v>122646806</v>
       </c>
       <c r="B7" t="n">
-        <v>74847</v>
+        <v>74863</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6439</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550565</v>
+        <v>550584</v>
       </c>
       <c r="R7" t="n">
-        <v>7244209</v>
+        <v>7244283</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122646806</v>
+        <v>122646801</v>
       </c>
       <c r="B8" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550584</v>
+        <v>550582</v>
       </c>
       <c r="R8" t="n">
-        <v>7244283</v>
+        <v>7244157</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122646801</v>
+        <v>122646800</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550582</v>
+        <v>550574</v>
       </c>
       <c r="R9" t="n">
-        <v>7244157</v>
+        <v>7244164</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122646799</v>
+        <v>122646798</v>
       </c>
       <c r="B10" t="n">
-        <v>79876</v>
+        <v>90962</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550558</v>
+        <v>550534</v>
       </c>
       <c r="R10" t="n">
-        <v>7244160</v>
+        <v>7244163</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122646804</v>
+        <v>122646809</v>
       </c>
       <c r="B11" t="n">
-        <v>90940</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550563</v>
+        <v>550583</v>
       </c>
       <c r="R11" t="n">
-        <v>7244202</v>
+        <v>7244281</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122646803</v>
+        <v>122646802</v>
       </c>
       <c r="B12" t="n">
-        <v>94756</v>
+        <v>74863</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,25 +1747,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2809</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550560</v>
+        <v>550583</v>
       </c>
       <c r="R12" t="n">
-        <v>7244169</v>
+        <v>7244155</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122646802</v>
+        <v>122646807</v>
       </c>
       <c r="B13" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550583</v>
+        <v>550585</v>
       </c>
       <c r="R13" t="n">
-        <v>7244155</v>
+        <v>7244284</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,6 +1917,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 56632-2024 artfynd.xlsx
+++ b/artfynd/A 56632-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122646819</v>
+        <v>122646805</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>74847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550649</v>
+        <v>550565</v>
       </c>
       <c r="R2" t="n">
-        <v>7244482</v>
+        <v>7244209</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122646804</v>
+        <v>122646807</v>
       </c>
       <c r="B3" t="n">
-        <v>90940</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550563</v>
+        <v>550585</v>
       </c>
       <c r="R3" t="n">
-        <v>7244202</v>
+        <v>7244284</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,6 +857,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122646805</v>
+        <v>122646798</v>
       </c>
       <c r="B4" t="n">
-        <v>74847</v>
+        <v>90962</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +904,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550565</v>
+        <v>550534</v>
       </c>
       <c r="R4" t="n">
-        <v>7244209</v>
+        <v>7244163</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122646799</v>
+        <v>122646800</v>
       </c>
       <c r="B5" t="n">
-        <v>79876</v>
+        <v>90962</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1010,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>550558</v>
+        <v>550574</v>
       </c>
       <c r="R5" t="n">
-        <v>7244160</v>
+        <v>7244164</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122646803</v>
+        <v>122646806</v>
       </c>
       <c r="B6" t="n">
-        <v>94756</v>
+        <v>74863</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1116,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2809</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550560</v>
+        <v>550584</v>
       </c>
       <c r="R6" t="n">
-        <v>7244169</v>
+        <v>7244283</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122646806</v>
+        <v>122646819</v>
       </c>
       <c r="B7" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550584</v>
+        <v>550649</v>
       </c>
       <c r="R7" t="n">
-        <v>7244283</v>
+        <v>7244482</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,7 +1316,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122646801</v>
+        <v>122646809</v>
       </c>
       <c r="B8" t="n">
         <v>78766</v>
@@ -1351,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550582</v>
+        <v>550583</v>
       </c>
       <c r="R8" t="n">
-        <v>7244157</v>
+        <v>7244281</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122646800</v>
+        <v>122646803</v>
       </c>
       <c r="B9" t="n">
-        <v>90962</v>
+        <v>94758</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,25 +1434,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>2809</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550574</v>
+        <v>550560</v>
       </c>
       <c r="R9" t="n">
-        <v>7244164</v>
+        <v>7244169</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122646798</v>
+        <v>122646801</v>
       </c>
       <c r="B10" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1544,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550534</v>
+        <v>550582</v>
       </c>
       <c r="R10" t="n">
-        <v>7244163</v>
+        <v>7244157</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122646809</v>
+        <v>122646804</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>90940</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1650,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550583</v>
+        <v>550563</v>
       </c>
       <c r="R11" t="n">
-        <v>7244281</v>
+        <v>7244202</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1841,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122646807</v>
+        <v>122646799</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>79876</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,25 +1858,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550585</v>
+        <v>550558</v>
       </c>
       <c r="R13" t="n">
-        <v>7244284</v>
+        <v>7244160</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,11 +1922,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 56632-2024 artfynd.xlsx
+++ b/artfynd/A 56632-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122646805</v>
+        <v>122646809</v>
       </c>
       <c r="B2" t="n">
-        <v>74847</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550565</v>
+        <v>550583</v>
       </c>
       <c r="R2" t="n">
-        <v>7244209</v>
+        <v>7244281</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122646807</v>
+        <v>122646799</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>79876</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550585</v>
+        <v>550558</v>
       </c>
       <c r="R3" t="n">
-        <v>7244284</v>
+        <v>7244160</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,11 +857,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122646798</v>
+        <v>122646800</v>
       </c>
       <c r="B4" t="n">
         <v>90962</v>
@@ -932,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550534</v>
+        <v>550574</v>
       </c>
       <c r="R4" t="n">
-        <v>7244163</v>
+        <v>7244164</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122646800</v>
+        <v>122646805</v>
       </c>
       <c r="B5" t="n">
-        <v>90962</v>
+        <v>74847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>550574</v>
+        <v>550565</v>
       </c>
       <c r="R5" t="n">
-        <v>7244164</v>
+        <v>7244209</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122646806</v>
+        <v>122646819</v>
       </c>
       <c r="B6" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550584</v>
+        <v>550649</v>
       </c>
       <c r="R6" t="n">
-        <v>7244283</v>
+        <v>7244482</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122646819</v>
+        <v>122646798</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550649</v>
+        <v>550534</v>
       </c>
       <c r="R7" t="n">
-        <v>7244482</v>
+        <v>7244163</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122646809</v>
+        <v>122646801</v>
       </c>
       <c r="B8" t="n">
         <v>78766</v>
@@ -1356,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550583</v>
+        <v>550582</v>
       </c>
       <c r="R8" t="n">
-        <v>7244281</v>
+        <v>7244157</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122646803</v>
+        <v>122646806</v>
       </c>
       <c r="B9" t="n">
-        <v>94758</v>
+        <v>74863</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,25 +1429,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2809</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550560</v>
+        <v>550584</v>
       </c>
       <c r="R9" t="n">
-        <v>7244169</v>
+        <v>7244283</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122646801</v>
+        <v>122646802</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550582</v>
+        <v>550583</v>
       </c>
       <c r="R10" t="n">
-        <v>7244157</v>
+        <v>7244155</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1740,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122646802</v>
+        <v>122646803</v>
       </c>
       <c r="B12" t="n">
-        <v>74863</v>
+        <v>94758</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,25 +1747,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>2809</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550583</v>
+        <v>550560</v>
       </c>
       <c r="R12" t="n">
-        <v>7244155</v>
+        <v>7244169</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122646799</v>
+        <v>122646807</v>
       </c>
       <c r="B13" t="n">
-        <v>79876</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,25 +1853,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550558</v>
+        <v>550585</v>
       </c>
       <c r="R13" t="n">
-        <v>7244160</v>
+        <v>7244284</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,6 +1917,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 56632-2024 artfynd.xlsx
+++ b/artfynd/A 56632-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122646809</v>
+        <v>122646807</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550583</v>
+        <v>550585</v>
       </c>
       <c r="R2" t="n">
-        <v>7244281</v>
+        <v>7244284</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122646799</v>
+        <v>122646804</v>
       </c>
       <c r="B3" t="n">
-        <v>79876</v>
+        <v>90948</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550558</v>
+        <v>550563</v>
       </c>
       <c r="R3" t="n">
-        <v>7244160</v>
+        <v>7244202</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122646800</v>
+        <v>122646809</v>
       </c>
       <c r="B4" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550574</v>
+        <v>550583</v>
       </c>
       <c r="R4" t="n">
-        <v>7244164</v>
+        <v>7244281</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122646805</v>
+        <v>122646798</v>
       </c>
       <c r="B5" t="n">
-        <v>74847</v>
+        <v>90970</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1010,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>550565</v>
+        <v>550534</v>
       </c>
       <c r="R5" t="n">
-        <v>7244209</v>
+        <v>7244163</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122646819</v>
+        <v>122646803</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>94766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1116,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550649</v>
+        <v>550560</v>
       </c>
       <c r="R6" t="n">
-        <v>7244482</v>
+        <v>7244169</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122646798</v>
+        <v>122646802</v>
       </c>
       <c r="B7" t="n">
-        <v>90962</v>
+        <v>74863</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550534</v>
+        <v>550583</v>
       </c>
       <c r="R7" t="n">
-        <v>7244163</v>
+        <v>7244155</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,7 +1316,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122646801</v>
+        <v>122646819</v>
       </c>
       <c r="B8" t="n">
         <v>78766</v>
@@ -1351,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550582</v>
+        <v>550649</v>
       </c>
       <c r="R8" t="n">
-        <v>7244157</v>
+        <v>7244482</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1523,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122646802</v>
+        <v>122646801</v>
       </c>
       <c r="B10" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1544,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550583</v>
+        <v>550582</v>
       </c>
       <c r="R10" t="n">
-        <v>7244155</v>
+        <v>7244157</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122646804</v>
+        <v>122646805</v>
       </c>
       <c r="B11" t="n">
-        <v>90940</v>
+        <v>74847</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1646,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>6439</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550563</v>
+        <v>550565</v>
       </c>
       <c r="R11" t="n">
-        <v>7244202</v>
+        <v>7244209</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122646803</v>
+        <v>122646800</v>
       </c>
       <c r="B12" t="n">
-        <v>94758</v>
+        <v>90970</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,25 +1752,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2809</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550560</v>
+        <v>550574</v>
       </c>
       <c r="R12" t="n">
-        <v>7244169</v>
+        <v>7244164</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122646807</v>
+        <v>122646799</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>79876</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,25 +1858,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550585</v>
+        <v>550558</v>
       </c>
       <c r="R13" t="n">
-        <v>7244284</v>
+        <v>7244160</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,11 +1922,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 56632-2024 artfynd.xlsx
+++ b/artfynd/A 56632-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122646807</v>
+        <v>122646803</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>94766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550585</v>
+        <v>550560</v>
       </c>
       <c r="R2" t="n">
-        <v>7244284</v>
+        <v>7244169</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122646804</v>
+        <v>122646801</v>
       </c>
       <c r="B3" t="n">
-        <v>90948</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550563</v>
+        <v>550582</v>
       </c>
       <c r="R3" t="n">
-        <v>7244202</v>
+        <v>7244157</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122646809</v>
+        <v>122646819</v>
       </c>
       <c r="B4" t="n">
         <v>78766</v>
@@ -932,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550583</v>
+        <v>550649</v>
       </c>
       <c r="R4" t="n">
-        <v>7244281</v>
+        <v>7244482</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122646798</v>
+        <v>122646802</v>
       </c>
       <c r="B5" t="n">
-        <v>90970</v>
+        <v>74863</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>550534</v>
+        <v>550583</v>
       </c>
       <c r="R5" t="n">
-        <v>7244163</v>
+        <v>7244155</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122646803</v>
+        <v>122646807</v>
       </c>
       <c r="B6" t="n">
-        <v>94766</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2809</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550560</v>
+        <v>550585</v>
       </c>
       <c r="R6" t="n">
-        <v>7244169</v>
+        <v>7244284</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,6 +1175,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122646802</v>
+        <v>122646799</v>
       </c>
       <c r="B7" t="n">
-        <v>74863</v>
+        <v>79876</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,25 +1222,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550583</v>
+        <v>550558</v>
       </c>
       <c r="R7" t="n">
-        <v>7244155</v>
+        <v>7244160</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122646819</v>
+        <v>122646806</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550649</v>
+        <v>550584</v>
       </c>
       <c r="R8" t="n">
-        <v>7244482</v>
+        <v>7244283</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122646806</v>
+        <v>122646809</v>
       </c>
       <c r="B9" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,21 +1438,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550584</v>
+        <v>550583</v>
       </c>
       <c r="R9" t="n">
-        <v>7244283</v>
+        <v>7244281</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122646801</v>
+        <v>122646800</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,21 +1544,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550582</v>
+        <v>550574</v>
       </c>
       <c r="R10" t="n">
-        <v>7244157</v>
+        <v>7244164</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1740,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122646800</v>
+        <v>122646804</v>
       </c>
       <c r="B12" t="n">
-        <v>90970</v>
+        <v>90948</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550574</v>
+        <v>550563</v>
       </c>
       <c r="R12" t="n">
-        <v>7244164</v>
+        <v>7244202</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122646799</v>
+        <v>122646798</v>
       </c>
       <c r="B13" t="n">
-        <v>79876</v>
+        <v>90970</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,25 +1858,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550558</v>
+        <v>550534</v>
       </c>
       <c r="R13" t="n">
-        <v>7244160</v>
+        <v>7244163</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 56632-2024 artfynd.xlsx
+++ b/artfynd/A 56632-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122646803</v>
+        <v>122646801</v>
       </c>
       <c r="B2" t="n">
-        <v>94766</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550560</v>
+        <v>550582</v>
       </c>
       <c r="R2" t="n">
-        <v>7244169</v>
+        <v>7244157</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122646801</v>
+        <v>122646803</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>94766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550582</v>
+        <v>550560</v>
       </c>
       <c r="R3" t="n">
-        <v>7244157</v>
+        <v>7244169</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 56632-2024 artfynd.xlsx
+++ b/artfynd/A 56632-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122646801</v>
+        <v>122646802</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550582</v>
+        <v>550583</v>
       </c>
       <c r="R2" t="n">
-        <v>7244157</v>
+        <v>7244155</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122646803</v>
+        <v>122646798</v>
       </c>
       <c r="B3" t="n">
-        <v>94766</v>
+        <v>90970</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2809</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550560</v>
+        <v>550534</v>
       </c>
       <c r="R3" t="n">
-        <v>7244169</v>
+        <v>7244163</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122646802</v>
+        <v>122646800</v>
       </c>
       <c r="B5" t="n">
-        <v>74863</v>
+        <v>90970</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>550583</v>
+        <v>550574</v>
       </c>
       <c r="R5" t="n">
-        <v>7244155</v>
+        <v>7244164</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122646807</v>
+        <v>122646809</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550585</v>
+        <v>550583</v>
       </c>
       <c r="R6" t="n">
-        <v>7244284</v>
+        <v>7244281</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,11 +1175,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122646799</v>
+        <v>122646807</v>
       </c>
       <c r="B7" t="n">
-        <v>79876</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550558</v>
+        <v>550585</v>
       </c>
       <c r="R7" t="n">
-        <v>7244160</v>
+        <v>7244284</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,6 +1281,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122646806</v>
+        <v>122646801</v>
       </c>
       <c r="B8" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550584</v>
+        <v>550582</v>
       </c>
       <c r="R8" t="n">
-        <v>7244283</v>
+        <v>7244157</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122646809</v>
+        <v>122646803</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>94766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,25 +1434,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550583</v>
+        <v>550560</v>
       </c>
       <c r="R9" t="n">
-        <v>7244281</v>
+        <v>7244169</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122646800</v>
+        <v>122646804</v>
       </c>
       <c r="B10" t="n">
-        <v>90970</v>
+        <v>90948</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,21 +1544,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550574</v>
+        <v>550563</v>
       </c>
       <c r="R10" t="n">
-        <v>7244164</v>
+        <v>7244202</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122646805</v>
+        <v>122646806</v>
       </c>
       <c r="B11" t="n">
-        <v>74847</v>
+        <v>74863</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,25 +1646,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6439</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550565</v>
+        <v>550584</v>
       </c>
       <c r="R11" t="n">
-        <v>7244209</v>
+        <v>7244283</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122646804</v>
+        <v>122646805</v>
       </c>
       <c r="B12" t="n">
-        <v>90948</v>
+        <v>74847</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,25 +1752,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>6439</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550563</v>
+        <v>550565</v>
       </c>
       <c r="R12" t="n">
-        <v>7244202</v>
+        <v>7244209</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122646798</v>
+        <v>122646799</v>
       </c>
       <c r="B13" t="n">
-        <v>90970</v>
+        <v>79876</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,25 +1858,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550534</v>
+        <v>550558</v>
       </c>
       <c r="R13" t="n">
-        <v>7244163</v>
+        <v>7244160</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 56632-2024 artfynd.xlsx
+++ b/artfynd/A 56632-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122646802</v>
+        <v>122646804</v>
       </c>
       <c r="B2" t="n">
-        <v>74863</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550583</v>
+        <v>550563</v>
       </c>
       <c r="R2" t="n">
-        <v>7244155</v>
+        <v>7244202</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122646798</v>
+        <v>122646803</v>
       </c>
       <c r="B3" t="n">
-        <v>90970</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>2809</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550534</v>
+        <v>550560</v>
       </c>
       <c r="R3" t="n">
-        <v>7244163</v>
+        <v>7244169</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,19 +877,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122646819</v>
+        <v>122646801</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -927,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550649</v>
+        <v>550582</v>
       </c>
       <c r="R4" t="n">
-        <v>7244482</v>
+        <v>7244157</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122646800</v>
+        <v>122646809</v>
       </c>
       <c r="B5" t="n">
-        <v>90970</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>550574</v>
+        <v>550583</v>
       </c>
       <c r="R5" t="n">
-        <v>7244164</v>
+        <v>7244281</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,19 +1079,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122646809</v>
+        <v>122646819</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1139,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550583</v>
+        <v>550649</v>
       </c>
       <c r="R6" t="n">
-        <v>7244281</v>
+        <v>7244482</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,37 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122646807</v>
+        <v>122646805</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550585</v>
+        <v>550565</v>
       </c>
       <c r="R7" t="n">
-        <v>7244284</v>
+        <v>7244209</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1251,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,15 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122646801</v>
+        <v>122646802</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,21 +1292,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550582</v>
+        <v>550583</v>
       </c>
       <c r="R8" t="n">
-        <v>7244157</v>
+        <v>7244155</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,37 +1382,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122646803</v>
+        <v>122646806</v>
       </c>
       <c r="B9" t="n">
-        <v>94766</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2809</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550560</v>
+        <v>550584</v>
       </c>
       <c r="R9" t="n">
-        <v>7244169</v>
+        <v>7244283</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,37 +1483,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122646804</v>
+        <v>122646799</v>
       </c>
       <c r="B10" t="n">
-        <v>90948</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550563</v>
+        <v>550558</v>
       </c>
       <c r="R10" t="n">
-        <v>7244202</v>
+        <v>7244160</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,15 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122646806</v>
+        <v>122646807</v>
       </c>
       <c r="B11" t="n">
-        <v>74863</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,21 +1595,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1674,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550584</v>
+        <v>550585</v>
       </c>
       <c r="R11" t="n">
-        <v>7244283</v>
+        <v>7244284</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1712,6 +1657,11 @@
           <t>2024-10-01</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1733,218 +1683,6 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr">
-        <is>
-          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>122646805</v>
-      </c>
-      <c r="B12" t="n">
-        <v>74847</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>6439</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Gulnål</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Chaenotheca brachypoda</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Dikanäs, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>550565</v>
-      </c>
-      <c r="R12" t="n">
-        <v>7244209</v>
-      </c>
-      <c r="S12" t="n">
-        <v>10</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Mika Thunell</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Robin Karlsson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>122646799</v>
-      </c>
-      <c r="B13" t="n">
-        <v>79876</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>6462</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Dikanäs, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>550558</v>
-      </c>
-      <c r="R13" t="n">
-        <v>7244160</v>
-      </c>
-      <c r="S13" t="n">
-        <v>10</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Mika Thunell</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Robin Karlsson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
         <is>
           <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
         </is>
